--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487020_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487020_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.153</v>
+        <v>7.2436</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8735</v>
+        <v>6.0828</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2795</v>
+        <v>1.1609</v>
       </c>
       <c r="G2" t="n">
         <v>1.4167</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0752</v>
+        <v>2.1658</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3562</v>
+        <v>0.5654</v>
       </c>
       <c r="U2" t="n">
-        <v>1.719</v>
+        <v>1.6004</v>
       </c>
       <c r="V2" t="n">
         <v>5.3038</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5096</v>
+        <v>5.0458</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0041</v>
+        <v>2.4811</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5054</v>
+        <v>2.5647</v>
       </c>
       <c r="G3" t="n">
         <v>2.4356</v>
@@ -688,13 +688,13 @@
         <v>0.8214</v>
       </c>
       <c r="S3" t="n">
-        <v>2.306</v>
+        <v>1.8423</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6464</v>
+        <v>1.1234</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6596</v>
+        <v>0.7189</v>
       </c>
       <c r="V3" t="n">
         <v>1.1786</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3482</v>
+        <v>3.3151</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2185</v>
+        <v>1.8001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1296</v>
+        <v>1.515</v>
       </c>
       <c r="G4" t="n">
         <v>4.3071</v>
@@ -766,13 +766,13 @@
         <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5935</v>
+        <v>1.5604</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0458</v>
+        <v>0.6274</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5476</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.9384</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0427</v>
+        <v>1.4325</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1556</v>
+        <v>-1.4695</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1984</v>
+        <v>2.9019</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4413</v>
@@ -844,13 +844,13 @@
         <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0302</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6197</v>
+        <v>0.3059</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4105</v>
+        <v>1.1141</v>
       </c>
       <c r="V5" t="n">
         <v>1.0698</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5567</v>
+        <v>0.4722</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7417</v>
+        <v>0.3766</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2984</v>
+        <v>0.0956</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7682</v>
+        <v>-0.0227</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0396</v>
+        <v>0.2693</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8077</v>
+        <v>-0.292</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8849</v>
+        <v>0.861</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1752</v>
+        <v>0.2954</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7097</v>
+        <v>0.5656</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1167</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2147</v>
+        <v>-0.0261</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.902</v>
+        <v>-0.8575</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4908</v>
+        <v>-0.2053</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7545</v>
+        <v>0.586</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1358</v>
+        <v>-0.279</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8903</v>
+        <v>0.8651</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1179</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1179</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5438</v>
+        <v>0.4102</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06279999999999999</v>
+        <v>-1.5325</v>
       </c>
       <c r="F7" t="n">
-        <v>0.481</v>
+        <v>1.9427</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0227</v>
+        <v>0.7682</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2693</v>
+        <v>-0.0396</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.292</v>
+        <v>0.8077</v>
       </c>
       <c r="J7" t="n">
-        <v>0.861</v>
+        <v>1.8849</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2954</v>
+        <v>0.1752</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5656</v>
+        <v>1.7097</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-1.1167</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0261</v>
+        <v>-0.2147</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8575</v>
+        <v>-0.902</v>
       </c>
       <c r="P7" t="n">
-        <v>0.616</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2053</v>
+        <v>-3.4908</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6576</v>
+        <v>1.608</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5928</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2504</v>
+        <v>1.5346</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.1179</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9881</v>
+        <v>-1.1118</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.616</v>
+        <v>-2.2436</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6279</v>
+        <v>1.1318</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0906</v>
@@ -1078,13 +1078,13 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1301</v>
+        <v>1.0064</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0731</v>
+        <v>0.4455</v>
       </c>
       <c r="U8" t="n">
-        <v>0.057</v>
+        <v>0.5609</v>
       </c>
       <c r="V8" t="n">
         <v>1.4098</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7793</v>
+        <v>-1.8996</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4074</v>
+        <v>0.1982</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1867</v>
+        <v>-2.0978</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1813</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6985</v>
+        <v>0.5782</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6392</v>
+        <v>0.43</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0593</v>
+        <v>0.1482</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2965</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2599</v>
+        <v>-2.5713</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8183</v>
+        <v>-3.9815</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5584</v>
+        <v>1.4102</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8656</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9474</v>
+        <v>1.636</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3721</v>
+        <v>0.4648</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3195</v>
+        <v>1.1713</v>
       </c>
       <c r="V10" t="n">
         <v>1.301</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4182</v>
+        <v>-4.6284</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.094</v>
+        <v>-4.571</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3242</v>
+        <v>-0.0574</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1539</v>
@@ -1312,13 +1312,13 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.291</v>
+        <v>0.4988</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3294</v>
+        <v>0.1937</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0384</v>
+        <v>0.3052</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.708499999999998</v>
+        <v>7.7083</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.859299999999998</v>
+        <v>-2.859299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>10.5677</v>
+        <v>10.5676</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8278</v>
@@ -1390,13 +1390,13 @@
         <v>10.2671</v>
       </c>
       <c r="S12" t="n">
-        <v>12.902</v>
+        <v>12.9019</v>
       </c>
       <c r="T12" t="n">
-        <v>3.950300000000001</v>
+        <v>3.9505</v>
       </c>
       <c r="U12" t="n">
-        <v>8.951599999999999</v>
+        <v>8.951700000000001</v>
       </c>
       <c r="V12" t="n">
         <v>7.9012</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7052</v>
+        <v>5.7435</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6675</v>
+        <v>4.9813</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0378</v>
+        <v>0.7622</v>
       </c>
       <c r="G13" t="n">
         <v>8.0884</v>
@@ -1468,13 +1468,13 @@
         <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2839</v>
+        <v>-1.2456</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4492</v>
+        <v>-1.1354</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1653</v>
+        <v>-0.1102</v>
       </c>
       <c r="V13" t="n">
         <v>-2.126</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1471</v>
+        <v>1.9867</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5959</v>
+        <v>1.1775</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5511</v>
+        <v>0.8092</v>
       </c>
       <c r="G14" t="n">
         <v>1.6203</v>
@@ -1546,13 +1546,13 @@
         <v>0.8214</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1767</v>
+        <v>-0.3371</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3021</v>
+        <v>-0.1163</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4788</v>
+        <v>-0.2208</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1179</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MUÑOZ QUIÑONES</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2181</v>
+        <v>0.76</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0965</v>
+        <v>-2.6789</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1215</v>
+        <v>3.4388</v>
       </c>
       <c r="G15" t="n">
-        <v>1.776</v>
+        <v>-1.325</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4914</v>
+        <v>0.3666</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7154</v>
+        <v>-1.6917</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9409</v>
+        <v>-1.3264</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8225</v>
+        <v>0.5553</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1184</v>
+        <v>-1.8817</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1649</v>
+        <v>0.0014</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3311</v>
+        <v>-0.1887</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8338</v>
+        <v>0.19</v>
       </c>
       <c r="P15" t="n">
+        <v>3.2855</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-0.4107</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.6427</v>
+        <v>3.6962</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2716</v>
+        <v>-1.4317</v>
       </c>
       <c r="T15" t="n">
-        <v>0.209</v>
+        <v>-1.182</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0626</v>
+        <v>-0.2497</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4189</v>
+        <v>0.2312</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4189</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0005</v>
+        <v>0.4405</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8421</v>
+        <v>-1.0012</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8426</v>
+        <v>1.4417</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.325</v>
+        <v>-0.5786</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3666</v>
+        <v>-1.7385</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6917</v>
+        <v>1.1599</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3264</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5553</v>
+        <v>-1.5207</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8817</v>
+        <v>0.7621</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0014</v>
+        <v>0.18</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1887</v>
+        <v>-0.2177</v>
       </c>
       <c r="O16" t="n">
-        <v>0.19</v>
+        <v>0.3977</v>
       </c>
       <c r="P16" t="n">
-        <v>3.2855</v>
+        <v>1.2321</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4107</v>
+        <v>-1.4374</v>
       </c>
       <c r="R16" t="n">
-        <v>3.6962</v>
+        <v>2.6694</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1911</v>
+        <v>-1.2737</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3452</v>
+        <v>-1.1625</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8459</v>
+        <v>-0.1112</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2312</v>
+        <v>1.0608</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2402</v>
+        <v>2.3573</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>V. MUÑOZ QUIÑONES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4644</v>
+        <v>0.2312</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4196</v>
+        <v>0.3643</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9553</v>
+        <v>-0.1331</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5786</v>
+        <v>1.776</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7385</v>
+        <v>2.4914</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1599</v>
+        <v>-0.7154</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7586000000000001</v>
+        <v>2.9409</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5207</v>
+        <v>2.8225</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7621</v>
+        <v>0.1184</v>
       </c>
       <c r="M17" t="n">
-        <v>0.18</v>
+        <v>-1.1649</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2177</v>
+        <v>-0.3311</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3977</v>
+        <v>-0.8338</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2321</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.4374</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6694</v>
+        <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1786</v>
+        <v>0.2847</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.5809</v>
+        <v>-0.5232</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5977</v>
+        <v>0.8079</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0608</v>
+        <v>-1.4189</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2965</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8965</v>
+        <v>-0.8076</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1617</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7348</v>
+        <v>-0.6458</v>
       </c>
       <c r="G18" t="n">
         <v>0.408</v>
@@ -1858,13 +1858,13 @@
         <v>0.4107</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6885</v>
+        <v>-0.5996</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3294</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3591</v>
+        <v>-0.2702</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4579</v>
+        <v>-1.0063</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8723</v>
+        <v>0.9769</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3302</v>
+        <v>-1.9832</v>
       </c>
       <c r="G19" t="n">
         <v>1.4059</v>
@@ -1936,13 +1936,13 @@
         <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.826</v>
+        <v>-1.3745</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9881</v>
+        <v>-0.8835</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.838</v>
+        <v>-0.491</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4751</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3927</v>
+        <v>-1.65</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1918</v>
+        <v>-0.6688</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2009</v>
+        <v>-0.9812</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6054</v>
@@ -2014,13 +2014,13 @@
         <v>3.0801</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.8407</v>
+        <v>-2.098</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.9762</v>
+        <v>-1.4531</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8646</v>
+        <v>-0.6449</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5893</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6165</v>
+        <v>-3.0394</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1008</v>
+        <v>-4.8916</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4843</v>
+        <v>1.8521</v>
       </c>
       <c r="G21" t="n">
         <v>-1.649</v>
@@ -2092,13 +2092,13 @@
         <v>3.0801</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2344</v>
+        <v>-1.6574</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.6082</v>
+        <v>-1.399</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6263</v>
+        <v>-0.2584</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3491</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.9514</v>
+        <v>-8.274900000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.9054</v>
+        <v>-7.487</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.046</v>
+        <v>-0.788</v>
       </c>
       <c r="G22" t="n">
         <v>-6.3128</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7536</v>
+        <v>-1.0771</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1857</v>
+        <v>-0.7673</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5679</v>
+        <v>-0.3098</v>
       </c>
       <c r="V22" t="n">
         <v>-2.117</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.708499999999999</v>
+        <v>-5.616300000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.389199999999999</v>
+        <v>-9.389200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6807</v>
+        <v>3.7727</v>
       </c>
       <c r="G23" t="n">
         <v>2.827799999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.118899999999998</v>
+        <v>-1.1189</v>
       </c>
       <c r="I23" t="n">
-        <v>3.9467</v>
+        <v>3.946699999999999</v>
       </c>
       <c r="J23" t="n">
         <v>4.503200000000001</v>
@@ -2236,7 +2236,7 @@
         <v>-2.0469</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3715000000000001</v>
+        <v>0.3714999999999998</v>
       </c>
       <c r="P23" t="n">
         <v>10.2672</v>
@@ -2248,19 +2248,19 @@
         <v>20.5342</v>
       </c>
       <c r="S23" t="n">
-        <v>-12.9019</v>
+        <v>-10.81</v>
       </c>
       <c r="T23" t="n">
-        <v>-8.9518</v>
+        <v>-8.951700000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.9504</v>
+        <v>-1.8583</v>
       </c>
       <c r="V23" t="n">
         <v>-7.9013</v>
       </c>
       <c r="W23" t="n">
-        <v>5.326300000000001</v>
+        <v>5.3263</v>
       </c>
       <c r="X23" t="n">
         <v>-13.2278</v>
